--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/COLORADO_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/COLORADO_2022.xlsx
@@ -2011,7 +2011,7 @@
         <v>9</v>
       </c>
       <c r="D92">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="93">
@@ -2119,7 +2119,7 @@
         <v>9</v>
       </c>
       <c r="D98">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="99">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C135">
@@ -3055,7 +3055,7 @@
         <v>9</v>
       </c>
       <c r="D150">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="151">
@@ -3379,7 +3379,7 @@
         <v>9</v>
       </c>
       <c r="D168">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="169">
@@ -3397,7 +3397,7 @@
         <v>9</v>
       </c>
       <c r="D169">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="170">
@@ -3433,7 +3433,7 @@
         <v>9</v>
       </c>
       <c r="D171">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="172">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C179">
@@ -3613,7 +3613,7 @@
         <v>9</v>
       </c>
       <c r="D181">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="182">
@@ -3631,7 +3631,7 @@
         <v>9</v>
       </c>
       <c r="D182">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="183">
@@ -3703,7 +3703,7 @@
         <v>9</v>
       </c>
       <c r="D186">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="187">
@@ -3757,7 +3757,7 @@
         <v>9</v>
       </c>
       <c r="D189">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="190">
@@ -4279,7 +4279,7 @@
         <v>9</v>
       </c>
       <c r="D218">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="219">
@@ -4567,7 +4567,7 @@
         <v>9</v>
       </c>
       <c r="D234">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="235">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C277">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C284">
@@ -5665,7 +5665,7 @@
         <v>9</v>
       </c>
       <c r="D295">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="296">
@@ -5719,7 +5719,7 @@
         <v>9</v>
       </c>
       <c r="D298">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="299">
@@ -6241,7 +6241,7 @@
         <v>9</v>
       </c>
       <c r="D327">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="328">
@@ -7087,7 +7087,7 @@
         <v>9</v>
       </c>
       <c r="D374">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="375">
@@ -8149,7 +8149,7 @@
         <v>9</v>
       </c>
       <c r="D433">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="434">
@@ -9031,7 +9031,7 @@
         <v>9</v>
       </c>
       <c r="D482">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="483">
@@ -9517,7 +9517,7 @@
         <v>9</v>
       </c>
       <c r="D509">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="510">
@@ -10003,7 +10003,7 @@
         <v>9</v>
       </c>
       <c r="D536">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="537">
@@ -12235,7 +12235,7 @@
         <v>9</v>
       </c>
       <c r="D660">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="661">
@@ -12361,7 +12361,7 @@
         <v>9</v>
       </c>
       <c r="D667">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="668">
@@ -12577,7 +12577,7 @@
         <v>9</v>
       </c>
       <c r="D679">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="680">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C695">
@@ -13855,7 +13855,7 @@
         <v>9</v>
       </c>
       <c r="D750">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="751">
@@ -15547,7 +15547,7 @@
         <v>9</v>
       </c>
       <c r="D844">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="845">
@@ -16051,7 +16051,7 @@
         <v>9</v>
       </c>
       <c r="D872">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="873">
@@ -16303,7 +16303,7 @@
         <v>9</v>
       </c>
       <c r="D886">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="887">
@@ -16987,7 +16987,7 @@
         <v>9</v>
       </c>
       <c r="D924">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="925">
@@ -18121,7 +18121,7 @@
         <v>9</v>
       </c>
       <c r="D987">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="988">
@@ -19075,7 +19075,7 @@
         <v>9</v>
       </c>
       <c r="D1040">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="1041">
@@ -19921,7 +19921,7 @@
         <v>9</v>
       </c>
       <c r="D1087">
-        <v>0.0009588749200937567</v>
+        <v>0.0009588749200937568</v>
       </c>
     </row>
     <row r="1088">
